--- a/docs/data/jp/xlsx/9962.xlsx
+++ b/docs/data/jp/xlsx/9962.xlsx
@@ -9835,7 +9835,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Reversal Of Provision For Loss On Business Liquidation EI</t>
+          <t>사업정리손실 충당금 환입액</t>
         </is>
       </c>
       <c r="C120" s="20" t="n">
@@ -12194,7 +12194,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>FABusinessesReportableSegmentsMember · Transactions With Other Segments</t>
+          <t>FABusinessesReportableSegmentsMember · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="C165" s="20" t="n">
@@ -12246,7 +12246,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>MoldComponentReportableSegmentsMember · Transactions With Other Segments</t>
+          <t>MoldComponentReportableSegmentsMember · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="D166" s="20" t="n">
@@ -12280,7 +12280,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>VONABusinessesReportableSegmentsMember · Transactions With Other Segments</t>
+          <t>VONABusinessesReportableSegmentsMember · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="C167" s="20" t="n">
@@ -12332,7 +12332,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>합계 · Transactions With Other Segments</t>
+          <t>합계 · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="C168" s="20" t="n">
@@ -12384,7 +12384,7 @@
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Transactions With Other Segments</t>
+          <t>조정액 · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="C169" s="20" t="n">
@@ -12436,7 +12436,7 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Transactions With Other Segments</t>
+          <t>EntityTotalMember · 부문 간 내부매출</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
@@ -12452,7 +12452,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>Transactions With Other Segments</t>
+          <t>부문 간 내부매출</t>
         </is>
       </c>
       <c r="C171" s="20" t="n">
@@ -13008,7 +13008,7 @@
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>FABusinessesReportableSegmentsMember · Operating Income</t>
+          <t>FABusinessesReportableSegmentsMember · 부문이익</t>
         </is>
       </c>
       <c r="C184" s="20" t="n">
@@ -13310,7 +13310,7 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>VONABusinessesReportableSegmentsMember · Operating Income</t>
+          <t>VONABusinessesReportableSegmentsMember · 부문이익</t>
         </is>
       </c>
       <c r="C190" s="20" t="n">
@@ -13490,7 +13490,7 @@
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>합계 · Operating Income</t>
+          <t>합계 · 부문이익</t>
         </is>
       </c>
       <c r="C193" s="20" t="n">
@@ -13670,7 +13670,7 @@
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Operating Income</t>
+          <t>조정액 · 부문이익</t>
         </is>
       </c>
       <c r="C196" s="20" t="n">
@@ -13738,7 +13738,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>부문이익</t>
         </is>
       </c>
       <c r="C198" s="12" t="n">
@@ -13841,7 +13841,7 @@
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>FABusinessesReportableSegmentsMember · Segment Income Before Amortization Of Goodwill</t>
+          <t>FABusinessesReportableSegmentsMember · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M201" s="20" t="n">
@@ -13854,7 +13854,7 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>MoldComponentReportableSegmentsMember · Segment Income Before Amortization Of Goodwill</t>
+          <t>MoldComponentReportableSegmentsMember · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M202" s="20" t="n">
@@ -13864,7 +13864,7 @@
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>VONABusinessesReportableSegmentsMember · Segment Income Before Amortization Of Goodwill</t>
+          <t>VONABusinessesReportableSegmentsMember · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M203" s="20" t="n">
@@ -13877,7 +13877,7 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>합계 · Segment Income Before Amortization Of Goodwill</t>
+          <t>합계 · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M204" s="20" t="n">
@@ -13890,7 +13890,7 @@
     <row r="205">
       <c r="A205" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Segment Income Before Amortization Of Goodwill</t>
+          <t>조정액 · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M205" s="20" t="n">
@@ -13903,7 +13903,7 @@
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Segment Income Before Amortization Of Goodwill</t>
+          <t>EntityTotalMember · 영업권 등 상각 전 부문이익</t>
         </is>
       </c>
       <c r="M206" s="20" t="n">
@@ -15081,7 +15081,7 @@
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>Reversal Of Provision For Loss On Business Liquidation Ope CF</t>
+          <t>사업정리손실 충당금 환입액</t>
         </is>
       </c>
       <c r="C226" s="20" t="n">
@@ -15214,7 +15214,7 @@
     <row r="230">
       <c r="A230" s="18" t="inlineStr">
         <is>
-          <t>Restructuring Losses Ope CF</t>
+          <t>사업재편손실</t>
         </is>
       </c>
       <c r="O230" s="20" t="n">
@@ -17423,7 +17423,7 @@
     <row r="267">
       <c r="A267" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Cash And Cash Equivalents Resulting From Fiscal Year Change Of Subsidiaries CF</t>
+          <t>연결자회사 결산기 변경에 따른 현금성자산 증감액</t>
         </is>
       </c>
       <c r="O267" s="20" t="n">
@@ -21542,7 +21542,7 @@
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>Provision For Office Transfer Expenses CL</t>
+          <t>사무소 이전비용 충당금</t>
         </is>
       </c>
       <c r="H115" s="20" t="n">
@@ -21719,7 +21719,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Business Liquidation NCL</t>
+          <t>사업정리손실 충당금</t>
         </is>
       </c>
       <c r="C121" s="20" t="n">
